--- a/output/stock_quant_scores/TSLA_income_df.xlsx
+++ b/output/stock_quant_scores/TSLA_income_df.xlsx
@@ -1262,7 +1262,9 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>6714000000</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1274,14 +1276,18 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>1.87</v>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
         <v>31000000</v>
       </c>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>5524000000</v>
+      </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
@@ -1298,9 +1304,13 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>13606000000</v>
+      </c>
       <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>53823000000</v>
+      </c>
       <c r="AV6" t="inlineStr"/>
     </row>
   </sheetData>
